--- a/BOM_Board1_Schematic1_2026-07-12.xlsx
+++ b/BOM_Board1_Schematic1_2026-07-12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="52">
   <si>
     <t>No.</t>
   </si>
@@ -85,6 +85,24 @@
     <t>3</t>
   </si>
   <si>
+    <t>AO3401A</t>
+  </si>
+  <si>
+    <t>Q1,Q2,Q3</t>
+  </si>
+  <si>
+    <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR</t>
+  </si>
+  <si>
+    <t>YTL(亚特联)</t>
+  </si>
+  <si>
+    <t>C53477312</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>4.7K</t>
   </si>
   <si>
@@ -97,7 +115,13 @@
     <t>10K</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>R8,R9,R10</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>LSM6DS3TR</t>
@@ -115,7 +139,7 @@
     <t>C95230</t>
   </si>
   <si>
-    <t>5</t>
+    <t>7</t>
   </si>
   <si>
     <t>BMP280</t>
@@ -133,7 +157,7 @@
     <t>C83291</t>
   </si>
   <si>
-    <t>6</t>
+    <t>8</t>
   </si>
   <si>
     <t>XIAO_ESP32_S3</t>
@@ -519,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="20" customWidth="1"/>
@@ -638,51 +662,51 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -690,67 +714,131 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" t="s">
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>42</v>
       </c>
-      <c r="E7" t="s">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>43</v>
       </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
     </row>
